--- a/Prestador/prontobaby/resultado/relatorio_prontobaby_APENAS_VALORES.xlsx
+++ b/Prestador/prontobaby/resultado/relatorio_prontobaby_APENAS_VALORES.xlsx
@@ -421,13 +421,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1" t="n">
         <v>0</v>
       </c>
       <c r="D1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" t="n">
         <v>0</v>
@@ -442,7 +442,7 @@
         <v>0</v>
       </c>
       <c r="I1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J1" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -573,13 +573,13 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -617,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -991,13 +991,13 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
